--- a/Tables/OSRI_Table1condensed.xlsx
+++ b/Tables/OSRI_Table1condensed.xlsx
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="F20">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
